--- a/customers/reza.xlsx
+++ b/customers/reza.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="249">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -760,6 +760,12 @@
   </si>
   <si>
     <t>1405/04/19</t>
+  </si>
+  <si>
+    <t>1405/06/27</t>
+  </si>
+  <si>
+    <t>چیپس سیگار</t>
   </si>
 </sst>
 </file>
@@ -1312,7 +1318,7 @@
       </c>
       <c r="H2" s="8">
         <f>B210</f>
-        <v>3475000</v>
+        <v>3715000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4338,17 +4344,23 @@
     <row r="206" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="7">
         <f t="shared" si="8"/>
-        <v>3475000</v>
-      </c>
-      <c r="B206" s="7"/>
+        <v>3715000</v>
+      </c>
+      <c r="B206" s="7">
+        <v>240000</v>
+      </c>
       <c r="C206" s="7"/>
-      <c r="D206" s="7"/>
-      <c r="E206" s="1"/>
+      <c r="D206" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="E206" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="7">
         <f t="shared" si="8"/>
-        <v>3475000</v>
+        <v>3715000</v>
       </c>
       <c r="B207" s="7"/>
       <c r="C207" s="7"/>
@@ -4358,7 +4370,7 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <f t="shared" si="8"/>
-        <v>3475000</v>
+        <v>3715000</v>
       </c>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -4369,7 +4381,7 @@
       <c r="A209" s="8"/>
       <c r="B209" s="8">
         <f xml:space="preserve"> SUM(B188:B208)+B183</f>
-        <v>21149000</v>
+        <v>21389000</v>
       </c>
       <c r="C209" s="8">
         <f>SUM(C188:C208)+C183</f>
@@ -4381,7 +4393,7 @@
       <c r="A210" s="8"/>
       <c r="B210" s="12">
         <f>A208</f>
-        <v>3475000</v>
+        <v>3715000</v>
       </c>
       <c r="C210" s="18" t="s">
         <v>244</v>

--- a/customers/reza.xlsx
+++ b/customers/reza.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="251">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -766,6 +766,12 @@
   </si>
   <si>
     <t>چیپس سیگار</t>
+  </si>
+  <si>
+    <t>1405/07/10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">چیپس  </t>
   </si>
 </sst>
 </file>
@@ -1318,7 +1324,7 @@
       </c>
       <c r="H2" s="8">
         <f>B210</f>
-        <v>3715000</v>
+        <v>3965000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4360,17 +4366,23 @@
     <row r="207" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="7">
         <f t="shared" si="8"/>
-        <v>3715000</v>
-      </c>
-      <c r="B207" s="7"/>
+        <v>3965000</v>
+      </c>
+      <c r="B207" s="7">
+        <v>250000</v>
+      </c>
       <c r="C207" s="7"/>
-      <c r="D207" s="7"/>
-      <c r="E207" s="1"/>
+      <c r="D207" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <f t="shared" si="8"/>
-        <v>3715000</v>
+        <v>3965000</v>
       </c>
       <c r="B208" s="7"/>
       <c r="C208" s="7"/>
@@ -4381,7 +4393,7 @@
       <c r="A209" s="8"/>
       <c r="B209" s="8">
         <f xml:space="preserve"> SUM(B188:B208)+B183</f>
-        <v>21389000</v>
+        <v>21639000</v>
       </c>
       <c r="C209" s="8">
         <f>SUM(C188:C208)+C183</f>
@@ -4393,7 +4405,7 @@
       <c r="A210" s="8"/>
       <c r="B210" s="12">
         <f>A208</f>
-        <v>3715000</v>
+        <v>3965000</v>
       </c>
       <c r="C210" s="18" t="s">
         <v>244</v>

--- a/customers/reza.xlsx
+++ b/customers/reza.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="253">
   <si>
     <t>نام طرف حساب :</t>
   </si>
@@ -772,6 +772,12 @@
   </si>
   <si>
     <t xml:space="preserve">چیپس  </t>
+  </si>
+  <si>
+    <t>1405/08/08</t>
+  </si>
+  <si>
+    <t>سیگارکیک رانی</t>
   </si>
 </sst>
 </file>
@@ -1324,7 +1330,7 @@
       </c>
       <c r="H2" s="8">
         <f>B210</f>
-        <v>3965000</v>
+        <v>4465000</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -4382,18 +4388,24 @@
     <row r="208" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <f t="shared" si="8"/>
-        <v>3965000</v>
-      </c>
-      <c r="B208" s="7"/>
+        <v>4465000</v>
+      </c>
+      <c r="B208" s="7">
+        <v>500000</v>
+      </c>
       <c r="C208" s="7"/>
-      <c r="D208" s="7"/>
-      <c r="E208" s="1"/>
+      <c r="D208" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="209" spans="1:4" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="8"/>
       <c r="B209" s="8">
         <f xml:space="preserve"> SUM(B188:B208)+B183</f>
-        <v>21639000</v>
+        <v>22139000</v>
       </c>
       <c r="C209" s="8">
         <f>SUM(C188:C208)+C183</f>
@@ -4405,7 +4417,7 @@
       <c r="A210" s="8"/>
       <c r="B210" s="12">
         <f>A208</f>
-        <v>3965000</v>
+        <v>4465000</v>
       </c>
       <c r="C210" s="18" t="s">
         <v>244</v>
